--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:37:23+00:00</t>
+    <t>2024-10-25T08:22:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T08:22:33+00:00</t>
+    <t>2024-10-28T11:11:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:11:19+00:00</t>
+    <t>2024-10-28T11:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:26:59+00:00</t>
+    <t>2024-10-29T09:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:20:35+00:00</t>
+    <t>2024-10-31T11:17:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T11:17:53+00:00</t>
+    <t>2024-10-31T15:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T15:29:56+00:00</t>
+    <t>2024-11-05T14:48:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T14:48:02+00:00</t>
+    <t>2024-11-07T21:06:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:06:19+00:00</t>
+    <t>2024-11-07T21:57:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:57:27+00:00</t>
+    <t>2024-11-07T22:09:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6384" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6384" uniqueCount="443">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-09T09:07:40+00:00</t>
+    <t>2024-11-11T13:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -608,8 +608,8 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:resource}
-</t>
+    <t>type:resource}
+profile:resolve()}</t>
   </si>
   <si>
     <t>open</t>
@@ -925,7 +925,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Encounter {http://example.org/StructureDefinition/MOPEDEncounter}
+    <t xml:space="preserve">Encounter {http://example.org/StructureDefinition/MOPEDEncounterKH}
 </t>
   </si>
   <si>
@@ -1278,6 +1278,19 @@
   </si>
   <si>
     <t>Bundle.entry:Hauptversicherter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelatedPerson {http://example.org/StructureDefinition/Hauptversicherter}
+</t>
+  </si>
+  <si>
+    <t>A person that is related to a patient, but who is not a direct target of care</t>
+  </si>
+  <si>
+    <t>Information about a person that is involved in a patient's health or the care for a patient, but who is not the target of healthcare, nor has a formal responsibility in the care process.</t>
+  </si>
+  <si>
+    <t>Entity, Role, or Act,role</t>
   </si>
   <si>
     <t>Bundle.entry:Hauptversicherter.search</t>
@@ -18744,7 +18757,7 @@
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -18763,13 +18776,13 @@
         <v>20</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>365</v>
+        <v>404</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -18841,15 +18854,15 @@
         <v>20</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>368</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>204</v>
@@ -18961,7 +18974,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>208</v>
@@ -19073,7 +19086,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>209</v>
@@ -19187,7 +19200,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>210</v>
@@ -19303,7 +19316,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>211</v>
@@ -19417,7 +19430,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>217</v>
@@ -19531,7 +19544,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>222</v>
@@ -19643,7 +19656,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>226</v>
@@ -19755,7 +19768,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>227</v>
@@ -19869,7 +19882,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>228</v>
@@ -19985,7 +19998,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>229</v>
@@ -20097,7 +20110,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>235</v>
@@ -20211,7 +20224,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>239</v>
@@ -20323,7 +20336,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>242</v>
@@ -20435,7 +20448,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>245</v>
@@ -20547,7 +20560,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>248</v>
@@ -20659,7 +20672,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>251</v>
@@ -20771,7 +20784,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>255</v>
@@ -20883,7 +20896,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>256</v>
@@ -20997,7 +21010,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>257</v>
@@ -21113,7 +21126,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>258</v>
@@ -21225,7 +21238,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>261</v>
@@ -21337,7 +21350,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>264</v>
@@ -21451,7 +21464,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>268</v>
@@ -21565,7 +21578,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>272</v>
@@ -21679,10 +21692,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -21705,19 +21718,19 @@
         <v>89</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>20</v>
@@ -21766,7 +21779,7 @@
         <v>20</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>77</v>
@@ -21795,10 +21808,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -21821,16 +21834,16 @@
         <v>89</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -21880,7 +21893,7 @@
         <v>20</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>77</v>
@@ -21889,7 +21902,7 @@
         <v>88</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>20</v>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:26:20+00:00</t>
+    <t>2024-11-12T06:42:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:42:28+00:00</t>
+    <t>2024-11-12T07:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:20:07+00:00</t>
+    <t>2024-11-12T07:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:35:41+00:00</t>
+    <t>2024-11-12T07:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:42:03+00:00</t>
+    <t>2024-11-12T08:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:38:00+00:00</t>
+    <t>2024-11-12T08:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:47:06+00:00</t>
+    <t>2024-11-12T20:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T20:06:39+00:00</t>
+    <t>2024-11-14T06:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T06:51:52+00:00</t>
+    <t>2024-11-14T14:31:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:31:22+00:00</t>
+    <t>2024-11-14T14:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:34:15+00:00</t>
+    <t>2024-11-14T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:43:46+00:00</t>
+    <t>2024-11-15T18:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T18:55:56+00:00</t>
+    <t>2024-11-15T19:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -608,8 +608,8 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
-    <t>type:resource}
-profile:resolve()}</t>
+    <t xml:space="preserve">profile:resolve()}
+</t>
   </si>
   <si>
     <t>open</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:04:50+00:00</t>
+    <t>2024-11-15T19:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -608,7 +608,7 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
-    <t xml:space="preserve">profile:resolve()}
+    <t xml:space="preserve">profile:resource.resolve()}
 </t>
   </si>
   <si>
@@ -1736,7 +1736,7 @@
     <col min="25" max="25" width="168.19140625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="49.01171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="25.36328125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:21:45+00:00</t>
+    <t>2024-11-15T20:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:14:47+00:00</t>
+    <t>2024-11-17T19:44:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -608,7 +608,7 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
-    <t xml:space="preserve">profile:resource.resolve()}
+    <t xml:space="preserve">profile:resource.resolve().meta.profile}
 </t>
   </si>
   <si>
@@ -1736,7 +1736,7 @@
     <col min="25" max="25" width="168.19140625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="49.01171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="25.36328125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="37.1171875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:44:33+00:00</t>
+    <t>2024-11-19T10:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T10:30:26+00:00</t>
+    <t>2025-02-10T09:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
